--- a/tables/eq51_53_54.xlsx
+++ b/tables/eq51_53_54.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AntFonseca\github\compare-time-series\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEFA687-816C-47E8-9229-A2A78333058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3016859B-B44D-488D-96E0-2E0465B06B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27521BE8-EDAD-44F8-A1B3-0260395A06E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27521BE8-EDAD-44F8-A1B3-0260395A06E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -170,9 +170,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -194,6 +191,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,37 +520,37 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -558,131 +558,131 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>2</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>5</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>4</v>
       </c>
-      <c r="E2" s="8">
-        <v>1</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="3">
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="2">
         <f>ABS(D2-B2)</f>
         <v>2</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <f>ABS(E2-C2)</f>
         <v>4</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>0</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>4</v>
       </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
         <v>5</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="3">
+      <c r="F3" s="9"/>
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G4" si="0">ABS(D3-B3)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <f t="shared" ref="H3:H4" si="1">ABS(E3-C3)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>5</v>
       </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="3">
+      <c r="F4" s="9"/>
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <f>SUM(B2:B4)</f>
         <v>7</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
         <v>10</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="4">
+      <c r="F5" s="9"/>
+      <c r="G5" s="3">
         <f>SUM(G2:G4)</f>
         <v>8</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <f>SUM(H2:H4)</f>
         <v>7</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <f>ABS(D5-B5)</f>
         <v>2</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <f>ABS(E5-C5)</f>
         <v>1</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <f>ABS(G5-I5)</f>
         <v>6</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="6">
         <f>ABS(H5-J5)</f>
         <v>6</v>
       </c>
@@ -691,17 +691,17 @@
       <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <f>(D4-D2)-(B4-B2)</f>
         <v>-7</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>(E4-E2)-(C4-C2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
@@ -719,12 +719,13 @@
         <f>ABS(H9-I9)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <f>J9+J10</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F10" s="10"/>
       <c r="G10" t="s">
         <v>17</v>
       </c>
@@ -740,9 +741,10 @@
         <f>ABS(H10-I10)</f>
         <v>6</v>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F11" s="10"/>
       <c r="G11" t="s">
         <v>18</v>
       </c>
@@ -758,12 +760,13 @@
         <f>ABS(H11-I11)</f>
         <v>5</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
         <f>J11+J12</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F12" s="10"/>
       <c r="G12" t="s">
         <v>19</v>
       </c>
@@ -779,7 +782,7 @@
         <f>ABS(H12-I12)</f>
         <v>1</v>
       </c>
-      <c r="K12" s="10"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G14">
@@ -897,10 +900,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="F1:F5"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="K11:K12"/>
+    <mergeCell ref="F9:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
